--- a/static/excel_templates/receipt_template.xlsx
+++ b/static/excel_templates/receipt_template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>접수번호</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -56,6 +56,10 @@
   <si>
     <t>재료명</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행상태</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -533,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1576"/>
+  <dimension ref="A1:I1576"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.125" style="12" customWidth="1"/>
@@ -544,9 +548,10 @@
     <col min="6" max="6" width="9.875" style="12" customWidth="1"/>
     <col min="7" max="7" width="13.125" style="12" customWidth="1"/>
     <col min="8" max="8" width="19.5" style="16" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24.95" customHeight="1">
+    <row r="1" spans="1:9" ht="24.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,8 +576,11 @@
       <c r="H1" s="19" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="3"/>
@@ -582,7 +590,7 @@
       <c r="G2" s="14"/>
       <c r="H2" s="20"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="3"/>
@@ -592,7 +600,7 @@
       <c r="G3" s="14"/>
       <c r="H3" s="20"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="3"/>
@@ -602,7 +610,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="20"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="3"/>
@@ -612,7 +620,7 @@
       <c r="G5" s="14"/>
       <c r="H5" s="20"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="3"/>
@@ -622,7 +630,7 @@
       <c r="G6" s="14"/>
       <c r="H6" s="20"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="3"/>
@@ -632,7 +640,7 @@
       <c r="G7" s="14"/>
       <c r="H7" s="20"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="3"/>
@@ -642,7 +650,7 @@
       <c r="G8" s="14"/>
       <c r="H8" s="20"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="3"/>
@@ -652,7 +660,7 @@
       <c r="G9" s="14"/>
       <c r="H9" s="20"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="3"/>
@@ -662,7 +670,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="20"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="3"/>
@@ -672,7 +680,7 @@
       <c r="G11" s="14"/>
       <c r="H11" s="20"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="3"/>
@@ -682,7 +690,7 @@
       <c r="G12" s="14"/>
       <c r="H12" s="20"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="3"/>
@@ -692,7 +700,7 @@
       <c r="G13" s="14"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="3"/>
@@ -702,7 +710,7 @@
       <c r="G14" s="14"/>
       <c r="H14" s="20"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="3"/>
@@ -712,7 +720,7 @@
       <c r="G15" s="14"/>
       <c r="H15" s="20"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="3"/>
